--- a/data/Can Transitions 8.9.26.xlsx
+++ b/data/Can Transitions 8.9.26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/angi_guthrie_alamancefoods_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{E84A7C08-1E40-499C-92F1-F4B050A4EE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E22D9017-6851-4E07-A1A3-3837C5700606}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{E84A7C08-1E40-499C-92F1-F4B050A4EE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4631B798-77EA-4195-8E37-F76FAF17A3B1}"/>
   <bookViews>
-    <workbookView xWindow="2256" yWindow="1644" windowWidth="34536" windowHeight="13728" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
+    <workbookView xWindow="11244" yWindow="-17472" windowWidth="30936" windowHeight="16776" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="81">
   <si>
     <t xml:space="preserve">ITEM CODE </t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>Favorite Day 12pk/13oz 19.5% Gingerbread</t>
+  </si>
+  <si>
+    <t>AS22</t>
   </si>
 </sst>
 </file>
@@ -379,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -393,12 +396,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -768,18 +765,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.59765625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.5546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="11" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -803,812 +800,826 @@
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="13">
         <v>12284</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="13">
         <v>12871</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="12" t="s">
+      <c r="F2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="13">
         <v>12279</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="13">
         <v>12872</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="12" t="s">
+      <c r="F3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <v>12227</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="13">
         <v>12846</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="12" t="s">
+      <c r="F4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="13">
         <v>12634</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="13">
         <v>12832</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="12" t="s">
+      <c r="F5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="13">
         <v>12340</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="13">
         <v>12838</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="F6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="13">
         <v>12291</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="13">
         <v>12816</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="13" t="s">
+      <c r="F7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="13">
         <v>12292</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="13">
         <v>12817</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="12" t="s">
+      <c r="F8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="13">
         <v>12293</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="13">
         <v>12818</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="12" t="s">
+      <c r="F9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="13">
         <v>12294</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="13">
         <v>12819</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="13">
         <v>12300</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="13">
         <v>12820</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="13">
         <v>12697</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="13">
         <v>12835</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="13" t="s">
+      <c r="F12" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="13">
         <v>12459</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="13">
         <v>12821</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="16">
         <v>12040</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="15">
+      <c r="D14" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="13">
         <v>12865</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="17" t="s">
+    <row r="15" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13">
         <v>12181</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="15">
+      <c r="D15" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="13">
         <v>12849</v>
       </c>
-      <c r="F15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="12" t="s">
+      <c r="F15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13">
         <v>12270</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="15">
+      <c r="D16" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="13">
         <v>12859</v>
       </c>
-      <c r="F16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="12" t="s">
+      <c r="F16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="13">
         <v>12760</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="13">
         <v>12895</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="13" t="s">
+      <c r="F17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="17" t="s">
+    <row r="18" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13">
         <v>12800</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="15">
+      <c r="D18" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="13">
         <v>12979</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="13">
         <v>12709</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="D19" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="13">
         <v>12823</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="12" t="s">
+      <c r="F19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13">
         <v>12767</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="D20" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="13">
         <v>12824</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="13" t="s">
+      <c r="F20" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="13">
         <v>12467</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="15">
+      <c r="D21" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="13">
         <v>12826</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="13" t="s">
+      <c r="F21" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13">
         <v>12468</v>
       </c>
-      <c r="D22" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="15">
+      <c r="D22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="13">
         <v>12827</v>
       </c>
-      <c r="F22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="13" t="s">
+      <c r="F22" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="17" t="s">
+    <row r="23" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13">
         <v>12052</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="15">
+      <c r="D23" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="13">
         <v>12783</v>
       </c>
-      <c r="F23" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="12" t="s">
+      <c r="F23" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="17" t="s">
+    <row r="24" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="13">
         <v>12053</v>
       </c>
-      <c r="D24" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="15">
+      <c r="D24" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="13">
         <v>12781</v>
       </c>
-      <c r="F24" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="F24" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="15" t="s">
+    <row r="25" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="13">
         <v>12054</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="15">
+      <c r="D25" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="13">
         <v>12782</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="13" t="s">
+      <c r="F25" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="11" t="s">
         <v>18</v>
       </c>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="13">
         <v>12054</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="15">
+      <c r="D26" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="13">
         <v>12893</v>
       </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="13"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="11"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="17" t="s">
+    <row r="27" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13">
         <v>12055</v>
       </c>
-      <c r="D27" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="13">
         <v>12780</v>
       </c>
-      <c r="F27" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="12" t="s">
+      <c r="F27" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="15" t="s">
+    <row r="28" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="16">
         <v>12385</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="D28" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="13">
         <v>12792</v>
       </c>
-      <c r="F28" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="13" t="s">
+      <c r="F28" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="15" t="s">
+    <row r="29" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="13">
         <v>12353</v>
       </c>
-      <c r="D29" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="15">
+      <c r="D29" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="13">
         <v>12866</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="13" t="s">
+      <c r="F29" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="15" t="s">
+    <row r="30" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="13">
         <v>12076</v>
       </c>
-      <c r="D30" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="15">
+      <c r="D30" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="13">
         <v>12869</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="13" t="s">
+      <c r="F30" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H30" s="5"/>
     </row>
-    <row r="31" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="15" t="s">
+    <row r="31" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="13">
         <v>12039</v>
       </c>
-      <c r="D31" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E31" s="15">
+      <c r="D31" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="13">
         <v>12870</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31" s="13" t="s">
+      <c r="F31" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="15" t="s">
+    <row r="32" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="13">
         <v>12401</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" s="15">
+      <c r="D32" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="13">
         <v>12867</v>
       </c>
-      <c r="F32" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32" s="13" t="s">
+      <c r="F32" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="5"/>
     </row>
-    <row r="33" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="15" t="s">
+    <row r="33" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="13">
         <v>12036</v>
       </c>
-      <c r="D33" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E33" s="15">
+      <c r="D33" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="13">
         <v>12868</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33" s="13" t="s">
+      <c r="F33" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H33" s="5"/>
     </row>
-    <row r="34" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="15" t="s">
+    <row r="34" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="13">
         <v>12278</v>
       </c>
-      <c r="D34" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" s="15">
+      <c r="D34" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="13">
         <v>12410</v>
       </c>
-      <c r="F34" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="13" t="s">
+      <c r="F34" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H34" s="5"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A35" s="8"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
+    <row r="35" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="13">
+        <v>12864</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="13">
+        <v>12020</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="H35" s="5"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A36" s="8"/>
-      <c r="B36" s="10"/>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="8"/>
+      <c r="D36" s="6"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
       <c r="H36" s="3"/>
     </row>
   </sheetData>

--- a/data/Can Transitions 8.9.26.xlsx
+++ b/data/Can Transitions 8.9.26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{E84A7C08-1E40-499C-92F1-F4B050A4EE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4631B798-77EA-4195-8E37-F76FAF17A3B1}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{E84A7C08-1E40-499C-92F1-F4B050A4EE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F977591C-4633-46ED-BBBF-2CED422CF9A2}"/>
   <bookViews>
-    <workbookView xWindow="11244" yWindow="-17472" windowWidth="30936" windowHeight="16776" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="79">
   <si>
     <t xml:space="preserve">ITEM CODE </t>
   </si>
@@ -153,12 +153,6 @@
   </si>
   <si>
     <t>Id Forsted Sugar Cookie  Cold Foam 6pk/14oz</t>
-  </si>
-  <si>
-    <t>AJ31</t>
-  </si>
-  <si>
-    <t>James Farm 12pk/15oz Light Whipped Cream</t>
   </si>
   <si>
     <t>Rolling Trans</t>
@@ -764,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" style="12" bestFit="1" customWidth="1"/>
@@ -1089,44 +1083,44 @@
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>38</v>
+      <c r="A14" s="15" t="s">
+        <v>39</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="16">
-        <v>12040</v>
+        <v>40</v>
+      </c>
+      <c r="C14" s="13">
+        <v>12181</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E14" s="13">
-        <v>12865</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>11</v>
+        <v>12849</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="13" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="13">
-        <v>12181</v>
+        <v>12270</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E15" s="13">
-        <v>12849</v>
+        <v>12859</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>10</v>
@@ -1144,64 +1138,64 @@
         <v>44</v>
       </c>
       <c r="C16" s="13">
-        <v>12270</v>
+        <v>12760</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E16" s="13">
-        <v>12859</v>
+        <v>12895</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>10</v>
+      <c r="G16" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>45</v>
+      <c r="A17" s="15" t="s">
+        <v>46</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="13">
-        <v>12760</v>
+        <v>12800</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E17" s="13">
-        <v>12895</v>
+        <v>12979</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>11</v>
+        <v>30</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="13">
-        <v>12800</v>
+        <v>12709</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E18" s="13">
-        <v>12979</v>
+        <v>12823</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>10</v>
@@ -1216,19 +1210,19 @@
         <v>51</v>
       </c>
       <c r="C19" s="13">
-        <v>12709</v>
+        <v>12767</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E19" s="13">
-        <v>12823</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>10</v>
+        <v>12824</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="H19" s="5"/>
     </row>
@@ -1240,13 +1234,13 @@
         <v>53</v>
       </c>
       <c r="C20" s="13">
-        <v>12767</v>
+        <v>12467</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E20" s="13">
-        <v>12824</v>
+        <v>12826</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>11</v>
@@ -1264,16 +1258,16 @@
         <v>55</v>
       </c>
       <c r="C21" s="13">
-        <v>12467</v>
+        <v>12468</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E21" s="13">
-        <v>12826</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>11</v>
+        <v>12827</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>11</v>
@@ -1281,26 +1275,26 @@
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="15" t="s">
         <v>56</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>57</v>
       </c>
       <c r="C22" s="13">
-        <v>12468</v>
+        <v>12052</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E22" s="13">
-        <v>12827</v>
+        <v>12783</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>11</v>
+      <c r="G22" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="H22" s="5"/>
     </row>
@@ -1312,13 +1306,13 @@
         <v>59</v>
       </c>
       <c r="C23" s="13">
-        <v>12052</v>
+        <v>12053</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E23" s="13">
-        <v>12783</v>
+        <v>12781</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>10</v>
@@ -1329,94 +1323,94 @@
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="13" t="s">
         <v>60</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="13">
-        <v>12053</v>
+        <v>12054</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E24" s="13">
-        <v>12781</v>
+        <v>12782</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>10</v>
+      <c r="G24" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C25" s="13">
         <v>12054</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E25" s="13">
-        <v>12782</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>18</v>
-      </c>
+        <v>12893</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="11"/>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="15" t="s">
         <v>62</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="13">
-        <v>12054</v>
+        <v>12055</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E26" s="13">
-        <v>12893</v>
-      </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="11"/>
+        <v>12780</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>10</v>
+      </c>
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="13" t="s">
         <v>64</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="13">
-        <v>12055</v>
+      <c r="C27" s="16">
+        <v>12385</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E27" s="13">
-        <v>12780</v>
+        <v>12792</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>10</v>
+      <c r="G27" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="H27" s="5"/>
     </row>
@@ -1427,17 +1421,17 @@
       <c r="B28" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="16">
-        <v>12385</v>
+      <c r="C28" s="13">
+        <v>12353</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E28" s="13">
-        <v>12792</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>10</v>
+        <v>12866</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>11</v>
@@ -1452,13 +1446,13 @@
         <v>69</v>
       </c>
       <c r="C29" s="13">
-        <v>12353</v>
+        <v>12076</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E29" s="13">
-        <v>12866</v>
+        <v>12869</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>11</v>
@@ -1476,13 +1470,13 @@
         <v>71</v>
       </c>
       <c r="C30" s="13">
-        <v>12076</v>
+        <v>12039</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E30" s="13">
-        <v>12869</v>
+        <v>12870</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>11</v>
@@ -1500,13 +1494,13 @@
         <v>73</v>
       </c>
       <c r="C31" s="13">
-        <v>12039</v>
+        <v>12401</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E31" s="13">
-        <v>12870</v>
+        <v>12867</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>11</v>
@@ -1524,13 +1518,13 @@
         <v>75</v>
       </c>
       <c r="C32" s="13">
-        <v>12401</v>
+        <v>12036</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E32" s="13">
-        <v>12867</v>
+        <v>12868</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>11</v>
@@ -1548,37 +1542,37 @@
         <v>77</v>
       </c>
       <c r="C33" s="13">
-        <v>12036</v>
+        <v>12278</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E33" s="13">
-        <v>12868</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>11</v>
+        <v>12410</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H33" s="5"/>
     </row>
-    <row r="34" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>78</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C34" s="13">
-        <v>12278</v>
+        <v>12864</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E34" s="13">
-        <v>12410</v>
+        <v>12020</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>10</v>
@@ -1588,39 +1582,15 @@
       </c>
       <c r="H34" s="5"/>
     </row>
-    <row r="35" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="13">
-        <v>12864</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="13">
-        <v>12020</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="3"/>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
